--- a/tools/importer/reports/import-nav.report.xlsx
+++ b/tools/importer/reports/import-nav.report.xlsx
@@ -82,7 +82,7 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-05T09:01:52.838Z</t>
+    <t>2026-10-06T10:01:59.133Z</t>
   </si>
 </sst>
 </file>
